--- a/templates/planilha-financeira-modelo.xlsx
+++ b/templates/planilha-financeira-modelo.xlsx
@@ -1214,7 +1214,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{241D28C0-40F4-4D2D-B45F-656C45B51D04}</x14:id>
+          <x14:id>{FE81FEE9-087B-4F3C-A0F8-BA1D0144C390}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1225,7 +1225,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{241D28C0-40F4-4D2D-B45F-656C45B51D04}">
+          <x14:cfRule type="dataBar" id="{FE81FEE9-087B-4F3C-A0F8-BA1D0144C390}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/templates/planilha-financeira-modelo.xlsx
+++ b/templates/planilha-financeira-modelo.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="101">
   <si>
     <t>Resumo financeiro</t>
   </si>
@@ -59,60 +59,63 @@
     <t>Dívidas em aberto</t>
   </si>
   <si>
+    <t>Combustível</t>
+  </si>
+  <si>
+    <t>Juros das dívidas por mês</t>
+  </si>
+  <si>
     <t>Contas da casa</t>
   </si>
   <si>
-    <t>Juros das dívidas por mês</t>
+    <t>Parcelas de dívidas por mês</t>
   </si>
   <si>
     <t>Saúde</t>
   </si>
   <si>
-    <t>Parcelas de dívidas por mês</t>
+    <t>Comprometimento da renda</t>
   </si>
   <si>
     <t>Educação</t>
   </si>
   <si>
-    <t>Comprometimento da renda</t>
+    <t>Patrimônio investido</t>
   </si>
   <si>
     <t>Lazer</t>
   </si>
   <si>
-    <t>Patrimônio investido</t>
+    <t>Aportes planejados por mês</t>
   </si>
   <si>
     <t>Assinaturas</t>
   </si>
   <si>
-    <t>Aportes planejados por mês</t>
-  </si>
-  <si>
     <t>Vestuário</t>
   </si>
   <si>
+    <t>Últimos 12 meses</t>
+  </si>
+  <si>
     <t>Pagamento de dívidas</t>
   </si>
   <si>
-    <t>Últimos 12 meses</t>
+    <t>Mês</t>
+  </si>
+  <si>
+    <t>Ganhos</t>
+  </si>
+  <si>
+    <t>Gastos</t>
+  </si>
+  <si>
+    <t>Saldo</t>
   </si>
   <si>
     <t>Investimentos</t>
   </si>
   <si>
-    <t>Mês</t>
-  </si>
-  <si>
-    <t>Ganhos</t>
-  </si>
-  <si>
-    <t>Gastos</t>
-  </si>
-  <si>
-    <t>Saldo</t>
-  </si>
-  <si>
     <t>Outros gastos</t>
   </si>
   <si>
@@ -297,6 +300,9 @@
   </si>
   <si>
     <t>Salário</t>
+  </si>
+  <si>
+    <t>Aplicativos (Uber, 99, iFood)</t>
   </si>
   <si>
     <t>Freelance / bico</t>
@@ -1026,7 +1032,7 @@
         <f>IF($B$5=0,0,G16/$B$5)</f>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f>EDATE($B$2,-11)</f>
       </c>
@@ -1038,6 +1044,15 @@
       </c>
       <c r="D17" s="6">
         <f>B17-C17</f>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="6">
+        <f>SUMIFS('Lançamentos'!$E:$E,'Lançamentos'!$D:$D,"Gasto",'Lançamentos'!$A:$A,"&gt;="&amp;$B$2,'Lançamentos'!$A:$A,"&lt;="&amp;$C$2,'Lançamentos'!$C:$C,F17)</f>
+      </c>
+      <c r="H17" s="7">
+        <f>IF($B$5=0,0,G17/$B$5)</f>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1196,7 +1211,7 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1220,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H16">
+  <conditionalFormatting sqref="H4:H17">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -1214,7 +1229,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{FE81FEE9-087B-4F3C-A0F8-BA1D0144C390}</x14:id>
+          <x14:id>{F2E309FA-E77D-474A-8B19-63D456D0D141}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1225,7 +1240,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{FE81FEE9-087B-4F3C-A0F8-BA1D0144C390}">
+          <x14:cfRule type="dataBar" id="{F2E309FA-E77D-474A-8B19-63D456D0D141}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -1235,7 +1250,7 @@
               </x14:cfvo>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H4:H16</xm:sqref>
+          <xm:sqref>H4:H17</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -1261,22 +1276,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="3:6" x14ac:dyDescent="0.25"/>
@@ -2283,10 +2298,10 @@
   <autoFilter ref="A1:F1"/>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C10:C1001">
-      <formula1>Listas!$B$2:$B$20</formula1>
+      <formula1>Listas!$B$2:$B$22</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C1001">
-      <formula1>Listas!$B$2:$B$20</formula1>
+      <formula1>Listas!$B$2:$B$22</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D10:D1001">
       <formula1>Listas!$A$2:$A$3</formula1>
@@ -2328,34 +2343,34 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
@@ -2804,40 +2819,40 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="L1" s="13" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
@@ -3262,7 +3277,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="26" customWidth="1"/>
@@ -3270,71 +3285,71 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -3342,13 +3357,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -3356,13 +3371,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -3370,13 +3385,13 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -3384,13 +3399,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -3398,10 +3413,10 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
@@ -3409,7 +3424,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -3417,7 +3432,7 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
@@ -3425,7 +3440,7 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
@@ -3445,7 +3460,7 @@
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
@@ -3471,6 +3486,16 @@
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
